--- a/public/sample.xlsx
+++ b/public/sample.xlsx
@@ -397,113 +397,1012 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:AO9"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>Full Name</v>
+        <v>Branch Name</v>
       </c>
       <c r="B1" t="str">
-        <v>Address</v>
+        <v>Transaction Date</v>
       </c>
       <c r="C1" t="str">
-        <v>PAN Card No</v>
+        <v>Caller Name</v>
       </c>
       <c r="D1" t="str">
+        <v>Donor Name</v>
+      </c>
+      <c r="E1" t="str">
+        <v>Mobile No</v>
+      </c>
+      <c r="F1" t="str">
+        <v>Len</v>
+      </c>
+      <c r="G1" t="str">
+        <v>Count</v>
+      </c>
+      <c r="H1" t="str">
+        <v>Mobile No-2/Tel</v>
+      </c>
+      <c r="I1" t="str">
+        <v>Len</v>
+      </c>
+      <c r="J1" t="str">
+        <v>Address1</v>
+      </c>
+      <c r="K1" t="str">
+        <v>Address2</v>
+      </c>
+      <c r="L1" t="str">
+        <v>Station</v>
+      </c>
+      <c r="M1" t="str">
+        <v>East/West</v>
+      </c>
+      <c r="N1" t="str">
+        <v>City</v>
+      </c>
+      <c r="O1" t="str">
+        <v>Pincode</v>
+      </c>
+      <c r="P1" t="str">
+        <v>Pan No</v>
+      </c>
+      <c r="Q1" t="str">
+        <v>Len</v>
+      </c>
+      <c r="R1" t="str">
+        <v>Mail Id</v>
+      </c>
+      <c r="S1" t="str">
+        <v>DOB</v>
+      </c>
+      <c r="T1" t="str">
+        <v>Data Category</v>
+      </c>
+      <c r="U1" t="str">
+        <v>Station</v>
+      </c>
+      <c r="V1" t="str">
+        <v>Mobile</v>
+      </c>
+      <c r="W1" t="str">
+        <v>Android No</v>
+      </c>
+      <c r="X1" t="str">
+        <v>Team</v>
+      </c>
+      <c r="Y1" t="str">
+        <v>Agent Name</v>
+      </c>
+      <c r="Z1" t="str">
+        <v>FSE Name</v>
+      </c>
+      <c r="AA1" t="str">
+        <v>MOP</v>
+      </c>
+      <c r="AB1" t="str">
+        <v>Received Bank</v>
+      </c>
+      <c r="AC1" t="str">
+        <v>Payment Id No</v>
+      </c>
+      <c r="AD1" t="str">
+        <v>Len</v>
+      </c>
+      <c r="AE1" t="str">
+        <v>Count</v>
+      </c>
+      <c r="AF1" t="str">
+        <v>Donor bank Name</v>
+      </c>
+      <c r="AG1" t="str">
         <v>Amount</v>
       </c>
-      <c r="E1" t="str">
-        <v>Payment Mode</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>Rahul Sharma</v>
-      </c>
-      <c r="B2" t="str">
-        <v>Mumbai, Maharashtra</v>
-      </c>
-      <c r="C2" t="str">
-        <v>ABCDE1234F</v>
-      </c>
-      <c r="D2">
-        <v>5000</v>
-      </c>
-      <c r="E2" t="str">
-        <v>UPI</v>
+      <c r="AH1" t="str">
+        <v>Reciept No</v>
+      </c>
+      <c r="AI1" t="str">
+        <v>Reciept Book no</v>
+      </c>
+      <c r="AJ1" t="str">
+        <v>Reciept date</v>
+      </c>
+      <c r="AK1" t="str">
+        <v>Time</v>
+      </c>
+      <c r="AL1" t="str">
+        <v>Project Supported</v>
+      </c>
+      <c r="AM1" t="str">
+        <v xml:space="preserve">Account of </v>
+      </c>
+      <c r="AN1" t="str">
+        <v>Remark 1</v>
+      </c>
+      <c r="AO1" t="str">
+        <v>Branch</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>Priya Patel</v>
+        <v>Mumbai</v>
       </c>
       <c r="B3" t="str">
-        <v>Ahmedabad, Gujarat</v>
+        <v>01-06-2026</v>
       </c>
       <c r="C3" t="str">
-        <v>FGHIJ5678K</v>
-      </c>
-      <c r="D3">
-        <v>12000</v>
+        <v>Amit Shah</v>
+      </c>
+      <c r="D3" t="str">
+        <v>Rahul Sharma</v>
       </c>
       <c r="E3" t="str">
-        <v>Bank Transfer</v>
+        <v>9876543210</v>
+      </c>
+      <c r="F3" t="str">
+        <v>10</v>
+      </c>
+      <c r="G3" t="str">
+        <v>1</v>
+      </c>
+      <c r="H3" t="str">
+        <v>9876543211</v>
+      </c>
+      <c r="I3" t="str">
+        <v>10</v>
+      </c>
+      <c r="J3" t="str">
+        <v>Flat 12, Sunshine Apartments</v>
+      </c>
+      <c r="K3" t="str">
+        <v>Andheri West</v>
+      </c>
+      <c r="L3" t="str">
+        <v>Andheri</v>
+      </c>
+      <c r="M3" t="str">
+        <v>West</v>
+      </c>
+      <c r="N3" t="str">
+        <v>Mumbai</v>
+      </c>
+      <c r="O3" t="str">
+        <v>400053</v>
+      </c>
+      <c r="P3" t="str">
+        <v>ABCDE1234F</v>
+      </c>
+      <c r="Q3" t="str">
+        <v>10</v>
+      </c>
+      <c r="R3" t="str">
+        <v>rahul.sharma@gmail.com</v>
+      </c>
+      <c r="S3" t="str">
+        <v>15-08-1985</v>
+      </c>
+      <c r="T3" t="str">
+        <v>Regular</v>
+      </c>
+      <c r="U3" t="str">
+        <v>Andheri</v>
+      </c>
+      <c r="V3" t="str">
+        <v>9876543210</v>
+      </c>
+      <c r="W3" t="str">
+        <v>ANd12345</v>
+      </c>
+      <c r="X3" t="str">
+        <v>Alpha Team</v>
+      </c>
+      <c r="Y3" t="str">
+        <v>Priya Singh</v>
+      </c>
+      <c r="Z3" t="str">
+        <v>Rajesh Kumar</v>
+      </c>
+      <c r="AA3" t="str">
+        <v>UPI</v>
+      </c>
+      <c r="AB3" t="str">
+        <v>HDFC Bank</v>
+      </c>
+      <c r="AC3" t="str">
+        <v>PAYID00123456</v>
+      </c>
+      <c r="AD3" t="str">
+        <v>12</v>
+      </c>
+      <c r="AE3" t="str">
+        <v>1</v>
+      </c>
+      <c r="AF3" t="str">
+        <v>HDFC Bank</v>
+      </c>
+      <c r="AG3" t="str">
+        <v>5000</v>
+      </c>
+      <c r="AH3" t="str">
+        <v>RCPT001</v>
+      </c>
+      <c r="AI3" t="str">
+        <v>NB001</v>
+      </c>
+      <c r="AJ3" t="str">
+        <v>01-06-2026</v>
+      </c>
+      <c r="AK3" t="str">
+        <v>10:30 AM</v>
+      </c>
+      <c r="AL3" t="str">
+        <v>Education</v>
+      </c>
+      <c r="AM3" t="str">
+        <v>Education Fund</v>
+      </c>
+      <c r="AN3" t="str">
+        <v>Thank you</v>
+      </c>
+      <c r="AO3" t="str">
+        <v>Mumbai</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Amit Singh</v>
+        <v>Delhi</v>
       </c>
       <c r="B4" t="str">
-        <v>New Delhi, Delhi</v>
+        <v>02-06-2026</v>
       </c>
       <c r="C4" t="str">
-        <v>KLMNO9012L</v>
-      </c>
-      <c r="D4">
-        <v>2500</v>
+        <v>Neha Gupta</v>
+      </c>
+      <c r="D4" t="str">
+        <v>Priya Patel</v>
       </c>
       <c r="E4" t="str">
-        <v>Cash</v>
+        <v>9876543220</v>
+      </c>
+      <c r="F4" t="str">
+        <v>10</v>
+      </c>
+      <c r="G4" t="str">
+        <v>2</v>
+      </c>
+      <c r="H4" t="str">
+        <v>9876543221</v>
+      </c>
+      <c r="I4" t="str">
+        <v>10</v>
+      </c>
+      <c r="J4" t="str">
+        <v>45, Green Park Colony</v>
+      </c>
+      <c r="K4" t="str">
+        <v>Green Park</v>
+      </c>
+      <c r="L4" t="str">
+        <v>Green Park</v>
+      </c>
+      <c r="M4" t="str">
+        <v>South</v>
+      </c>
+      <c r="N4" t="str">
+        <v>Delhi</v>
+      </c>
+      <c r="O4" t="str">
+        <v>110016</v>
+      </c>
+      <c r="P4" t="str">
+        <v>FGHIJ5678K</v>
+      </c>
+      <c r="Q4" t="str">
+        <v>10</v>
+      </c>
+      <c r="R4" t="str">
+        <v>priya.patel@yahoo.com</v>
+      </c>
+      <c r="S4" t="str">
+        <v>22-03-1990</v>
+      </c>
+      <c r="T4" t="str">
+        <v>New</v>
+      </c>
+      <c r="U4" t="str">
+        <v>Green Park</v>
+      </c>
+      <c r="V4" t="str">
+        <v>9876543220</v>
+      </c>
+      <c r="W4" t="str">
+        <v>ANd67890</v>
+      </c>
+      <c r="X4" t="str">
+        <v>Beta Team</v>
+      </c>
+      <c r="Y4" t="str">
+        <v>Amit Verma</v>
+      </c>
+      <c r="Z4" t="str">
+        <v>Sunita Yadav</v>
+      </c>
+      <c r="AA4" t="str">
+        <v>Credit Card</v>
+      </c>
+      <c r="AB4" t="str">
+        <v>ICICI Bank</v>
+      </c>
+      <c r="AC4" t="str">
+        <v>CCID00234567</v>
+      </c>
+      <c r="AD4" t="str">
+        <v>12</v>
+      </c>
+      <c r="AE4" t="str">
+        <v>1</v>
+      </c>
+      <c r="AF4" t="str">
+        <v>ICICI Bank</v>
+      </c>
+      <c r="AG4" t="str">
+        <v>12000</v>
+      </c>
+      <c r="AH4" t="str">
+        <v>RCPT002</v>
+      </c>
+      <c r="AI4" t="str">
+        <v>NB001</v>
+      </c>
+      <c r="AJ4" t="str">
+        <v>02-06-2026</v>
+      </c>
+      <c r="AK4" t="str">
+        <v>11:15 AM</v>
+      </c>
+      <c r="AL4" t="str">
+        <v>Healthcare</v>
+      </c>
+      <c r="AM4" t="str">
+        <v>Health Fund</v>
+      </c>
+      <c r="AN4" t="str">
+        <v>For medical camp</v>
+      </c>
+      <c r="AO4" t="str">
+        <v>Delhi</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>Sneha Reddy</v>
+        <v>Pune</v>
       </c>
       <c r="B5" t="str">
-        <v>Hyderabad, Telangana</v>
+        <v>03-06-2026</v>
       </c>
       <c r="C5" t="str">
-        <v>PQRST3456M</v>
-      </c>
-      <c r="D5">
-        <v>100000</v>
+        <v>Suresh Iyer</v>
+      </c>
+      <c r="D5" t="str">
+        <v>Amit Verma</v>
       </c>
       <c r="E5" t="str">
-        <v>Cheque</v>
+        <v>9876543230</v>
+      </c>
+      <c r="F5" t="str">
+        <v>10</v>
+      </c>
+      <c r="G5" t="str">
+        <v>3</v>
+      </c>
+      <c r="H5" t="str">
+        <v>9876543231</v>
+      </c>
+      <c r="I5" t="str">
+        <v>10</v>
+      </c>
+      <c r="J5" t="str">
+        <v>201, Lake Vista Society</v>
+      </c>
+      <c r="K5" t="str">
+        <v>Kothrud</v>
+      </c>
+      <c r="L5" t="str">
+        <v>Kothrud</v>
+      </c>
+      <c r="M5" t="str">
+        <v>East</v>
+      </c>
+      <c r="N5" t="str">
+        <v>Pune</v>
+      </c>
+      <c r="O5" t="str">
+        <v>411038</v>
+      </c>
+      <c r="P5" t="str">
+        <v>KLMNO9012P</v>
+      </c>
+      <c r="Q5" t="str">
+        <v>10</v>
+      </c>
+      <c r="R5" t="str">
+        <v>amit.verma@outlook.com</v>
+      </c>
+      <c r="S5" t="str">
+        <v>10-11-1978</v>
+      </c>
+      <c r="T5" t="str">
+        <v>Regular</v>
+      </c>
+      <c r="U5" t="str">
+        <v>Kothrud</v>
+      </c>
+      <c r="V5" t="str">
+        <v>9876543230</v>
+      </c>
+      <c r="W5" t="str">
+        <v>ANd34567</v>
+      </c>
+      <c r="X5" t="str">
+        <v>Gamma Team</v>
+      </c>
+      <c r="Y5" t="str">
+        <v>Rohan Joshi</v>
+      </c>
+      <c r="Z5" t="str">
+        <v>Meera Nair</v>
+      </c>
+      <c r="AA5" t="str">
+        <v>Net Banking</v>
+      </c>
+      <c r="AB5" t="str">
+        <v>SBI</v>
+      </c>
+      <c r="AC5" t="str">
+        <v>NBID00345678</v>
+      </c>
+      <c r="AD5" t="str">
+        <v>12</v>
+      </c>
+      <c r="AE5" t="str">
+        <v>1</v>
+      </c>
+      <c r="AF5" t="str">
+        <v>State Bank of India</v>
+      </c>
+      <c r="AG5" t="str">
+        <v>25000</v>
+      </c>
+      <c r="AH5" t="str">
+        <v>RCPT003</v>
+      </c>
+      <c r="AI5" t="str">
+        <v>NB002</v>
+      </c>
+      <c r="AJ5" t="str">
+        <v>03-06-2026</v>
+      </c>
+      <c r="AK5" t="str">
+        <v>09:45 AM</v>
+      </c>
+      <c r="AL5" t="str">
+        <v>Child Welfare</v>
+      </c>
+      <c r="AM5" t="str">
+        <v>Child Welfare Fund</v>
+      </c>
+      <c r="AN5" t="str">
+        <v>Monthly donation</v>
+      </c>
+      <c r="AO5" t="str">
+        <v>Pune</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>Vikram Joshi</v>
+        <v>Chennai</v>
       </c>
       <c r="B6" t="str">
-        <v>Pune, Maharashtra</v>
+        <v>04-06-2026</v>
       </c>
       <c r="C6" t="str">
-        <v>UVWXY7890N</v>
-      </c>
-      <c r="D6">
-        <v>75000</v>
+        <v>Lakshmi Narayan</v>
+      </c>
+      <c r="D6" t="str">
+        <v>Sundar Rajan</v>
       </c>
       <c r="E6" t="str">
+        <v>9876543240</v>
+      </c>
+      <c r="F6" t="str">
+        <v>10</v>
+      </c>
+      <c r="G6" t="str">
+        <v>4</v>
+      </c>
+      <c r="H6" t="str">
+        <v>9876543241</v>
+      </c>
+      <c r="I6" t="str">
+        <v>10</v>
+      </c>
+      <c r="J6" t="str">
+        <v>7, Temple View Road</v>
+      </c>
+      <c r="K6" t="str">
+        <v>Mylapore</v>
+      </c>
+      <c r="L6" t="str">
+        <v>Mylapore</v>
+      </c>
+      <c r="M6" t="str">
+        <v>East</v>
+      </c>
+      <c r="N6" t="str">
+        <v>Chennai</v>
+      </c>
+      <c r="O6" t="str">
+        <v>600004</v>
+      </c>
+      <c r="P6" t="str">
+        <v>PQRST3456L</v>
+      </c>
+      <c r="Q6" t="str">
+        <v>10</v>
+      </c>
+      <c r="R6" t="str">
+        <v>sundar.rajan@gmail.com</v>
+      </c>
+      <c r="S6" t="str">
+        <v>05-07-1982</v>
+      </c>
+      <c r="T6" t="str">
+        <v>Regular</v>
+      </c>
+      <c r="U6" t="str">
+        <v>Mylapore</v>
+      </c>
+      <c r="V6" t="str">
+        <v>9876543240</v>
+      </c>
+      <c r="W6" t="str">
+        <v>ANd90123</v>
+      </c>
+      <c r="X6" t="str">
+        <v>Delta Team</v>
+      </c>
+      <c r="Y6" t="str">
+        <v>Karthik Subramaniam</v>
+      </c>
+      <c r="Z6" t="str">
+        <v>Anitha Devi</v>
+      </c>
+      <c r="AA6" t="str">
+        <v>Cheque</v>
+      </c>
+      <c r="AB6" t="str">
+        <v>Indian Bank</v>
+      </c>
+      <c r="AC6" t="str">
+        <v>CHQ00456789</v>
+      </c>
+      <c r="AD6" t="str">
+        <v>12</v>
+      </c>
+      <c r="AE6" t="str">
+        <v>1</v>
+      </c>
+      <c r="AF6" t="str">
+        <v>Indian Bank</v>
+      </c>
+      <c r="AG6" t="str">
+        <v>8000</v>
+      </c>
+      <c r="AH6" t="str">
+        <v>RCPT004</v>
+      </c>
+      <c r="AI6" t="str">
+        <v>NB002</v>
+      </c>
+      <c r="AJ6" t="str">
+        <v>04-06-2026</v>
+      </c>
+      <c r="AK6" t="str">
+        <v>02:00 PM</v>
+      </c>
+      <c r="AL6" t="str">
+        <v>Education</v>
+      </c>
+      <c r="AM6" t="str">
+        <v>Education Fund</v>
+      </c>
+      <c r="AN6" t="str">
+        <v>Scholarship donation</v>
+      </c>
+      <c r="AO6" t="str">
+        <v>Chennai</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>Bangalore</v>
+      </c>
+      <c r="B7" t="str">
+        <v>05-06-2026</v>
+      </c>
+      <c r="C7" t="str">
+        <v>Arun Kumar</v>
+      </c>
+      <c r="D7" t="str">
+        <v>Divya Shetty</v>
+      </c>
+      <c r="E7" t="str">
+        <v>9876543250</v>
+      </c>
+      <c r="F7" t="str">
+        <v>10</v>
+      </c>
+      <c r="G7" t="str">
+        <v>5</v>
+      </c>
+      <c r="H7" t="str">
+        <v>9876543251</v>
+      </c>
+      <c r="I7" t="str">
+        <v>10</v>
+      </c>
+      <c r="J7" t="str">
+        <v>88, Tech Park Residency</v>
+      </c>
+      <c r="K7" t="str">
+        <v>Whitefield</v>
+      </c>
+      <c r="L7" t="str">
+        <v>Whitefield</v>
+      </c>
+      <c r="M7" t="str">
+        <v>East</v>
+      </c>
+      <c r="N7" t="str">
+        <v>Bangalore</v>
+      </c>
+      <c r="O7" t="str">
+        <v>560066</v>
+      </c>
+      <c r="P7" t="str">
+        <v>UVWXY7890M</v>
+      </c>
+      <c r="Q7" t="str">
+        <v>10</v>
+      </c>
+      <c r="R7" t="str">
+        <v>divya.shetty@gmail.com</v>
+      </c>
+      <c r="S7" t="str">
+        <v>18-12-1995</v>
+      </c>
+      <c r="T7" t="str">
+        <v>New</v>
+      </c>
+      <c r="U7" t="str">
+        <v>Whitefield</v>
+      </c>
+      <c r="V7" t="str">
+        <v>9876543250</v>
+      </c>
+      <c r="W7" t="str">
+        <v>ANd56789</v>
+      </c>
+      <c r="X7" t="str">
+        <v>Alpha Team</v>
+      </c>
+      <c r="Y7" t="str">
+        <v>Vikram Patel</v>
+      </c>
+      <c r="Z7" t="str">
+        <v>Sneha Reddy</v>
+      </c>
+      <c r="AA7" t="str">
         <v>UPI</v>
+      </c>
+      <c r="AB7" t="str">
+        <v>Kotak Mahindra</v>
+      </c>
+      <c r="AC7" t="str">
+        <v>PAYID00567890</v>
+      </c>
+      <c r="AD7" t="str">
+        <v>12</v>
+      </c>
+      <c r="AE7" t="str">
+        <v>1</v>
+      </c>
+      <c r="AF7" t="str">
+        <v>Kotak Mahindra Bank</v>
+      </c>
+      <c r="AG7" t="str">
+        <v>15000</v>
+      </c>
+      <c r="AH7" t="str">
+        <v>RCPT005</v>
+      </c>
+      <c r="AI7" t="str">
+        <v>NB003</v>
+      </c>
+      <c r="AJ7" t="str">
+        <v>05-06-2026</v>
+      </c>
+      <c r="AK7" t="str">
+        <v>04:30 PM</v>
+      </c>
+      <c r="AL7" t="str">
+        <v>Environment</v>
+      </c>
+      <c r="AM7" t="str">
+        <v>Environment Fund</v>
+      </c>
+      <c r="AN7" t="str">
+        <v>Tree plantation drive</v>
+      </c>
+      <c r="AO7" t="str">
+        <v>Bangalore</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>Kolkata</v>
+      </c>
+      <c r="B8" t="str">
+        <v>06-06-2026</v>
+      </c>
+      <c r="C8" t="str">
+        <v>Mita Banerjee</v>
+      </c>
+      <c r="D8" t="str">
+        <v>Animesh Das</v>
+      </c>
+      <c r="E8" t="str">
+        <v>9876543260</v>
+      </c>
+      <c r="F8" t="str">
+        <v>10</v>
+      </c>
+      <c r="G8" t="str">
+        <v>6</v>
+      </c>
+      <c r="H8" t="str">
+        <v>9876543261</v>
+      </c>
+      <c r="I8" t="str">
+        <v>10</v>
+      </c>
+      <c r="J8" t="str">
+        <v>16, Riverside Avenue</v>
+      </c>
+      <c r="K8" t="str">
+        <v>Salt Lake</v>
+      </c>
+      <c r="L8" t="str">
+        <v>Salt Lake</v>
+      </c>
+      <c r="M8" t="str">
+        <v>West</v>
+      </c>
+      <c r="N8" t="str">
+        <v>Kolkata</v>
+      </c>
+      <c r="O8" t="str">
+        <v>700091</v>
+      </c>
+      <c r="P8" t="str">
+        <v>ZABCD1234N</v>
+      </c>
+      <c r="Q8" t="str">
+        <v>10</v>
+      </c>
+      <c r="R8" t="str">
+        <v>animesh.das@rediffmail.com</v>
+      </c>
+      <c r="S8" t="str">
+        <v>30-09-1988</v>
+      </c>
+      <c r="T8" t="str">
+        <v>Regular</v>
+      </c>
+      <c r="U8" t="str">
+        <v>Salt Lake</v>
+      </c>
+      <c r="V8" t="str">
+        <v>9876543260</v>
+      </c>
+      <c r="W8" t="str">
+        <v>ANd12389</v>
+      </c>
+      <c r="X8" t="str">
+        <v>Gamma Team</v>
+      </c>
+      <c r="Y8" t="str">
+        <v>Rajat Ghosh</v>
+      </c>
+      <c r="Z8" t="str">
+        <v>Poulami Sen</v>
+      </c>
+      <c r="AA8" t="str">
+        <v>Credit Card</v>
+      </c>
+      <c r="AB8" t="str">
+        <v>Axis Bank</v>
+      </c>
+      <c r="AC8" t="str">
+        <v>CCID00678901</v>
+      </c>
+      <c r="AD8" t="str">
+        <v>12</v>
+      </c>
+      <c r="AE8" t="str">
+        <v>1</v>
+      </c>
+      <c r="AF8" t="str">
+        <v>Axis Bank</v>
+      </c>
+      <c r="AG8" t="str">
+        <v>3000</v>
+      </c>
+      <c r="AH8" t="str">
+        <v>RCPT006</v>
+      </c>
+      <c r="AI8" t="str">
+        <v>NB003</v>
+      </c>
+      <c r="AJ8" t="str">
+        <v>06-06-2026</v>
+      </c>
+      <c r="AK8" t="str">
+        <v>10:00 AM</v>
+      </c>
+      <c r="AL8" t="str">
+        <v>Healthcare</v>
+      </c>
+      <c r="AM8" t="str">
+        <v>Health Fund</v>
+      </c>
+      <c r="AN8" t="str">
+        <v>For medical equipment</v>
+      </c>
+      <c r="AO8" t="str">
+        <v>Kolkata</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>Ahmedabad</v>
+      </c>
+      <c r="B9" t="str">
+        <v>07-06-2026</v>
+      </c>
+      <c r="C9" t="str">
+        <v>Karan Patel</v>
+      </c>
+      <c r="D9" t="str">
+        <v>Mehul Shah</v>
+      </c>
+      <c r="E9" t="str">
+        <v>9876543270</v>
+      </c>
+      <c r="F9" t="str">
+        <v>10</v>
+      </c>
+      <c r="G9" t="str">
+        <v>7</v>
+      </c>
+      <c r="H9" t="str">
+        <v/>
+      </c>
+      <c r="I9" t="str">
+        <v>0</v>
+      </c>
+      <c r="J9" t="str">
+        <v>302, Business Hub</v>
+      </c>
+      <c r="K9" t="str">
+        <v>Navrangpura</v>
+      </c>
+      <c r="L9" t="str">
+        <v>Navrangpura</v>
+      </c>
+      <c r="M9" t="str">
+        <v>West</v>
+      </c>
+      <c r="N9" t="str">
+        <v>Ahmedabad</v>
+      </c>
+      <c r="O9" t="str">
+        <v>380009</v>
+      </c>
+      <c r="P9" t="str">
+        <v/>
+      </c>
+      <c r="Q9" t="str">
+        <v>0</v>
+      </c>
+      <c r="R9" t="str">
+        <v/>
+      </c>
+      <c r="S9" t="str">
+        <v>14-05-1975</v>
+      </c>
+      <c r="T9" t="str">
+        <v>Regular</v>
+      </c>
+      <c r="U9" t="str">
+        <v>Navrangpura</v>
+      </c>
+      <c r="V9" t="str">
+        <v>9876543270</v>
+      </c>
+      <c r="W9" t="str">
+        <v>ANd45678</v>
+      </c>
+      <c r="X9" t="str">
+        <v>Beta Team</v>
+      </c>
+      <c r="Y9" t="str">
+        <v>Nidhi Patel</v>
+      </c>
+      <c r="Z9" t="str">
+        <v>Jayesh Desai</v>
+      </c>
+      <c r="AA9" t="str">
+        <v>Cash</v>
+      </c>
+      <c r="AB9" t="str">
+        <v>SBI</v>
+      </c>
+      <c r="AC9" t="str">
+        <v>CASH00789012</v>
+      </c>
+      <c r="AD9" t="str">
+        <v>12</v>
+      </c>
+      <c r="AE9" t="str">
+        <v>1</v>
+      </c>
+      <c r="AF9" t="str">
+        <v>State Bank of India</v>
+      </c>
+      <c r="AG9" t="str">
+        <v>50000</v>
+      </c>
+      <c r="AH9" t="str">
+        <v>RCPT007</v>
+      </c>
+      <c r="AI9" t="str">
+        <v>NB004</v>
+      </c>
+      <c r="AJ9" t="str">
+        <v>07-06-2026</v>
+      </c>
+      <c r="AK9" t="str">
+        <v>12:00 PM</v>
+      </c>
+      <c r="AL9" t="str">
+        <v>Women Empowerment</v>
+      </c>
+      <c r="AM9" t="str">
+        <v>Women Empowerment Fund</v>
+      </c>
+      <c r="AN9" t="str">
+        <v>Annual donation</v>
+      </c>
+      <c r="AO9" t="str">
+        <v>Ahmedabad</v>
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E6"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:AO9"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/public/sample.xlsx
+++ b/public/sample.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="327" uniqueCount="216">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="281" uniqueCount="194">
   <si>
     <t>Branch Name</t>
   </si>
@@ -124,97 +124,31 @@
     <t>Branch</t>
   </si>
   <si>
-    <t>Mumbai</t>
-  </si>
-  <si>
-    <t>01-06-2026</t>
-  </si>
-  <si>
-    <t>Amit Shah</t>
-  </si>
-  <si>
-    <t>Rahul Sharma</t>
-  </si>
-  <si>
-    <t>9876543210</t>
-  </si>
-  <si>
     <t>10</t>
   </si>
   <si>
     <t>1</t>
   </si>
   <si>
-    <t>9876543211</t>
-  </si>
-  <si>
-    <t>Flat 12, Sunshine Apartments</t>
-  </si>
-  <si>
-    <t>Andheri West</t>
-  </si>
-  <si>
-    <t>Andheri</t>
-  </si>
-  <si>
     <t>West</t>
   </si>
   <si>
-    <t>400053</t>
-  </si>
-  <si>
-    <t>ABCDE1234F</t>
-  </si>
-  <si>
-    <t>rahul.sharma@gmail.com</t>
-  </si>
-  <si>
-    <t>15-08-1985</t>
-  </si>
-  <si>
     <t>Regular</t>
   </si>
   <si>
-    <t>ANd12345</t>
-  </si>
-  <si>
     <t>Alpha Team</t>
   </si>
   <si>
-    <t>Priya Singh</t>
-  </si>
-  <si>
-    <t>Rajesh Kumar</t>
-  </si>
-  <si>
     <t>UPI</t>
   </si>
   <si>
-    <t>HDFC Bank</t>
-  </si>
-  <si>
-    <t>PAYID00123456</t>
-  </si>
-  <si>
     <t>12</t>
   </si>
   <si>
-    <t>5000</t>
-  </si>
-  <si>
-    <t>RCPT001</t>
-  </si>
-  <si>
     <t>NB001</t>
   </si>
   <si>
-    <t>10:30 AM</t>
-  </si>
-  <si>
     <t>Education</t>
-  </si>
-  <si>
-    <t>Thank you</t>
   </si>
   <si>
     <t>Delhi</t>
@@ -1036,16 +970,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AO9"/>
+  <dimension ref="A1:AO10"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
+    <col min="4" max="4" width="12.625" customWidth="1"/>
     <col min="8" max="8" width="12.375" customWidth="1"/>
     <col min="10" max="10" width="25.375" customWidth="1"/>
     <col min="22" max="22" width="10.375" customWidth="1"/>
+    <col min="26" max="26" width="12.25" customWidth="1"/>
     <col min="29" max="29" width="13.375" customWidth="1"/>
     <col min="34" max="34" width="11.25" customWidth="1"/>
     <col min="35" max="35" width="11.125" customWidth="1"/>
-    <col min="36" max="36" width="13" customWidth="1"/>
+    <col min="36" max="36" width="13.875" customWidth="1"/>
     <col min="39" max="39" width="14.5" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1175,884 +1111,765 @@
       </c>
     </row>
     <row r="3" spans="1:41" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>36</v>
-      </c>
-      <c r="B3" t="s">
-        <v>37</v>
-      </c>
-      <c r="C3" t="s">
-        <v>38</v>
-      </c>
-      <c r="D3" t="s">
-        <v>39</v>
-      </c>
-      <c r="E3" t="s">
-        <v>40</v>
-      </c>
-      <c r="F3" t="s">
-        <v>41</v>
-      </c>
-      <c r="G3" t="s">
-        <v>42</v>
-      </c>
-      <c r="H3" t="s">
-        <v>43</v>
-      </c>
-      <c r="I3" t="s">
-        <v>41</v>
-      </c>
-      <c r="J3" t="s">
-        <v>44</v>
-      </c>
-      <c r="K3" t="s">
-        <v>45</v>
-      </c>
-      <c r="L3" t="s">
-        <v>46</v>
-      </c>
-      <c r="M3" t="s">
-        <v>47</v>
-      </c>
-      <c r="N3" t="s">
-        <v>36</v>
-      </c>
-      <c r="O3" t="s">
-        <v>48</v>
-      </c>
-      <c r="P3" t="s">
-        <v>49</v>
-      </c>
-      <c r="Q3" t="s">
-        <v>41</v>
-      </c>
-      <c r="R3" t="s">
-        <v>50</v>
-      </c>
-      <c r="S3" t="s">
-        <v>51</v>
-      </c>
-      <c r="T3" t="s">
-        <v>52</v>
-      </c>
-      <c r="U3" t="s">
-        <v>46</v>
-      </c>
-      <c r="V3" t="s">
-        <v>40</v>
-      </c>
-      <c r="W3" t="s">
-        <v>53</v>
-      </c>
-      <c r="X3" t="s">
-        <v>54</v>
-      </c>
-      <c r="Y3" t="s">
-        <v>55</v>
-      </c>
-      <c r="Z3" t="s">
-        <v>56</v>
-      </c>
-      <c r="AA3" t="s">
-        <v>57</v>
-      </c>
-      <c r="AB3" t="s">
-        <v>58</v>
-      </c>
-      <c r="AC3" t="s">
-        <v>59</v>
-      </c>
-      <c r="AD3" t="s">
-        <v>60</v>
-      </c>
-      <c r="AE3" t="s">
-        <v>42</v>
-      </c>
-      <c r="AF3" t="s">
-        <v>58</v>
-      </c>
-      <c r="AG3" t="s">
-        <v>61</v>
-      </c>
-      <c r="AH3" t="s">
-        <v>62</v>
-      </c>
-      <c r="AI3" t="s">
-        <v>63</v>
-      </c>
-      <c r="AJ3" s="1">
-        <v>46174</v>
-      </c>
-      <c r="AK3" t="s">
-        <v>64</v>
-      </c>
-      <c r="AL3" t="s">
-        <v>65</v>
-      </c>
-      <c r="AM3" t="s">
-        <v>215</v>
-      </c>
-      <c r="AN3" t="s">
-        <v>66</v>
-      </c>
-      <c r="AO3" t="s">
-        <v>36</v>
-      </c>
+      <c r="AJ3" s="1"/>
     </row>
     <row r="4" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
+        <v>45</v>
+      </c>
+      <c r="B4" t="s">
+        <v>46</v>
+      </c>
+      <c r="C4" t="s">
+        <v>47</v>
+      </c>
+      <c r="D4" t="s">
+        <v>48</v>
+      </c>
+      <c r="E4" t="s">
+        <v>49</v>
+      </c>
+      <c r="F4" t="s">
+        <v>36</v>
+      </c>
+      <c r="G4" t="s">
+        <v>50</v>
+      </c>
+      <c r="H4" t="s">
+        <v>51</v>
+      </c>
+      <c r="I4" t="s">
+        <v>36</v>
+      </c>
+      <c r="J4" t="s">
+        <v>52</v>
+      </c>
+      <c r="K4" t="s">
+        <v>53</v>
+      </c>
+      <c r="L4" t="s">
+        <v>53</v>
+      </c>
+      <c r="M4" t="s">
+        <v>54</v>
+      </c>
+      <c r="N4" t="s">
+        <v>45</v>
+      </c>
+      <c r="O4" t="s">
+        <v>55</v>
+      </c>
+      <c r="P4" t="s">
+        <v>56</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>36</v>
+      </c>
+      <c r="R4" t="s">
+        <v>57</v>
+      </c>
+      <c r="S4" t="s">
+        <v>58</v>
+      </c>
+      <c r="T4" t="s">
+        <v>59</v>
+      </c>
+      <c r="U4" t="s">
+        <v>53</v>
+      </c>
+      <c r="V4" t="s">
+        <v>49</v>
+      </c>
+      <c r="W4" t="s">
+        <v>60</v>
+      </c>
+      <c r="X4" t="s">
+        <v>61</v>
+      </c>
+      <c r="Y4" t="s">
+        <v>62</v>
+      </c>
+      <c r="Z4" t="s">
+        <v>63</v>
+      </c>
+      <c r="AA4" t="s">
+        <v>64</v>
+      </c>
+      <c r="AB4" t="s">
+        <v>65</v>
+      </c>
+      <c r="AC4" t="s">
+        <v>66</v>
+      </c>
+      <c r="AD4" t="s">
+        <v>42</v>
+      </c>
+      <c r="AE4" t="s">
+        <v>37</v>
+      </c>
+      <c r="AF4" t="s">
+        <v>65</v>
+      </c>
+      <c r="AG4" t="s">
         <v>67</v>
       </c>
-      <c r="B4" t="s">
+      <c r="AH4" t="s">
         <v>68</v>
       </c>
-      <c r="C4" t="s">
+      <c r="AI4" t="s">
+        <v>43</v>
+      </c>
+      <c r="AJ4" s="1">
+        <v>46175</v>
+      </c>
+      <c r="AK4" t="s">
         <v>69</v>
       </c>
-      <c r="D4" t="s">
+      <c r="AL4" t="s">
         <v>70</v>
       </c>
-      <c r="E4" t="s">
+      <c r="AM4" t="s">
+        <v>193</v>
+      </c>
+      <c r="AN4" t="s">
         <v>71</v>
       </c>
-      <c r="F4" t="s">
-        <v>41</v>
-      </c>
-      <c r="G4" t="s">
-        <v>72</v>
-      </c>
-      <c r="H4" t="s">
-        <v>73</v>
-      </c>
-      <c r="I4" t="s">
-        <v>41</v>
-      </c>
-      <c r="J4" t="s">
-        <v>74</v>
-      </c>
-      <c r="K4" t="s">
-        <v>75</v>
-      </c>
-      <c r="L4" t="s">
-        <v>75</v>
-      </c>
-      <c r="M4" t="s">
-        <v>76</v>
-      </c>
-      <c r="N4" t="s">
-        <v>67</v>
-      </c>
-      <c r="O4" t="s">
-        <v>77</v>
-      </c>
-      <c r="P4" t="s">
-        <v>78</v>
-      </c>
-      <c r="Q4" t="s">
-        <v>41</v>
-      </c>
-      <c r="R4" t="s">
-        <v>79</v>
-      </c>
-      <c r="S4" t="s">
-        <v>80</v>
-      </c>
-      <c r="T4" t="s">
-        <v>81</v>
-      </c>
-      <c r="U4" t="s">
-        <v>75</v>
-      </c>
-      <c r="V4" t="s">
-        <v>71</v>
-      </c>
-      <c r="W4" t="s">
-        <v>82</v>
-      </c>
-      <c r="X4" t="s">
-        <v>83</v>
-      </c>
-      <c r="Y4" t="s">
-        <v>84</v>
-      </c>
-      <c r="Z4" t="s">
-        <v>85</v>
-      </c>
-      <c r="AA4" t="s">
-        <v>86</v>
-      </c>
-      <c r="AB4" t="s">
-        <v>87</v>
-      </c>
-      <c r="AC4" t="s">
-        <v>88</v>
-      </c>
-      <c r="AD4" t="s">
-        <v>60</v>
-      </c>
-      <c r="AE4" t="s">
-        <v>42</v>
-      </c>
-      <c r="AF4" t="s">
-        <v>87</v>
-      </c>
-      <c r="AG4" t="s">
-        <v>89</v>
-      </c>
-      <c r="AH4" t="s">
-        <v>90</v>
-      </c>
-      <c r="AI4" t="s">
-        <v>63</v>
-      </c>
-      <c r="AJ4" t="s">
-        <v>68</v>
-      </c>
-      <c r="AK4" t="s">
-        <v>91</v>
-      </c>
-      <c r="AL4" t="s">
-        <v>92</v>
-      </c>
-      <c r="AM4" t="s">
-        <v>215</v>
-      </c>
-      <c r="AN4" t="s">
-        <v>93</v>
-      </c>
       <c r="AO4" t="s">
-        <v>67</v>
+        <v>45</v>
       </c>
     </row>
     <row r="5" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
+        <v>72</v>
+      </c>
+      <c r="B5" t="s">
+        <v>73</v>
+      </c>
+      <c r="C5" t="s">
+        <v>74</v>
+      </c>
+      <c r="D5" t="s">
+        <v>62</v>
+      </c>
+      <c r="E5" t="s">
+        <v>75</v>
+      </c>
+      <c r="F5" t="s">
+        <v>36</v>
+      </c>
+      <c r="G5" t="s">
+        <v>76</v>
+      </c>
+      <c r="H5" t="s">
+        <v>77</v>
+      </c>
+      <c r="I5" t="s">
+        <v>36</v>
+      </c>
+      <c r="J5" t="s">
+        <v>78</v>
+      </c>
+      <c r="K5" t="s">
+        <v>79</v>
+      </c>
+      <c r="L5" t="s">
+        <v>79</v>
+      </c>
+      <c r="M5" t="s">
+        <v>80</v>
+      </c>
+      <c r="N5" t="s">
+        <v>72</v>
+      </c>
+      <c r="O5" t="s">
+        <v>81</v>
+      </c>
+      <c r="P5" t="s">
+        <v>82</v>
+      </c>
+      <c r="Q5" t="s">
+        <v>36</v>
+      </c>
+      <c r="R5" t="s">
+        <v>83</v>
+      </c>
+      <c r="S5" t="s">
+        <v>84</v>
+      </c>
+      <c r="T5" t="s">
+        <v>39</v>
+      </c>
+      <c r="U5" t="s">
+        <v>79</v>
+      </c>
+      <c r="V5" t="s">
+        <v>75</v>
+      </c>
+      <c r="W5" t="s">
+        <v>85</v>
+      </c>
+      <c r="X5" t="s">
+        <v>86</v>
+      </c>
+      <c r="Y5" t="s">
+        <v>87</v>
+      </c>
+      <c r="Z5" t="s">
+        <v>88</v>
+      </c>
+      <c r="AA5" t="s">
+        <v>89</v>
+      </c>
+      <c r="AB5" t="s">
+        <v>90</v>
+      </c>
+      <c r="AC5" t="s">
+        <v>91</v>
+      </c>
+      <c r="AD5" t="s">
+        <v>42</v>
+      </c>
+      <c r="AE5" t="s">
+        <v>37</v>
+      </c>
+      <c r="AF5" t="s">
+        <v>92</v>
+      </c>
+      <c r="AG5" t="s">
+        <v>93</v>
+      </c>
+      <c r="AH5" t="s">
         <v>94</v>
       </c>
-      <c r="B5" t="s">
+      <c r="AI5" t="s">
         <v>95</v>
       </c>
-      <c r="C5" t="s">
+      <c r="AJ5" s="1">
+        <v>46176</v>
+      </c>
+      <c r="AK5" t="s">
         <v>96</v>
       </c>
-      <c r="D5" t="s">
-        <v>84</v>
-      </c>
-      <c r="E5" t="s">
+      <c r="AL5" t="s">
         <v>97</v>
       </c>
-      <c r="F5" t="s">
-        <v>41</v>
-      </c>
-      <c r="G5" t="s">
+      <c r="AM5" t="s">
+        <v>193</v>
+      </c>
+      <c r="AN5" t="s">
         <v>98</v>
       </c>
-      <c r="H5" t="s">
-        <v>99</v>
-      </c>
-      <c r="I5" t="s">
-        <v>41</v>
-      </c>
-      <c r="J5" t="s">
-        <v>100</v>
-      </c>
-      <c r="K5" t="s">
-        <v>101</v>
-      </c>
-      <c r="L5" t="s">
-        <v>101</v>
-      </c>
-      <c r="M5" t="s">
-        <v>102</v>
-      </c>
-      <c r="N5" t="s">
-        <v>94</v>
-      </c>
-      <c r="O5" t="s">
-        <v>103</v>
-      </c>
-      <c r="P5" t="s">
-        <v>104</v>
-      </c>
-      <c r="Q5" t="s">
-        <v>41</v>
-      </c>
-      <c r="R5" t="s">
-        <v>105</v>
-      </c>
-      <c r="S5" t="s">
-        <v>106</v>
-      </c>
-      <c r="T5" t="s">
-        <v>52</v>
-      </c>
-      <c r="U5" t="s">
-        <v>101</v>
-      </c>
-      <c r="V5" t="s">
-        <v>97</v>
-      </c>
-      <c r="W5" t="s">
-        <v>107</v>
-      </c>
-      <c r="X5" t="s">
-        <v>108</v>
-      </c>
-      <c r="Y5" t="s">
-        <v>109</v>
-      </c>
-      <c r="Z5" t="s">
-        <v>110</v>
-      </c>
-      <c r="AA5" t="s">
-        <v>111</v>
-      </c>
-      <c r="AB5" t="s">
-        <v>112</v>
-      </c>
-      <c r="AC5" t="s">
-        <v>113</v>
-      </c>
-      <c r="AD5" t="s">
-        <v>60</v>
-      </c>
-      <c r="AE5" t="s">
-        <v>42</v>
-      </c>
-      <c r="AF5" t="s">
-        <v>114</v>
-      </c>
-      <c r="AG5" t="s">
-        <v>115</v>
-      </c>
-      <c r="AH5" t="s">
-        <v>116</v>
-      </c>
-      <c r="AI5" t="s">
-        <v>117</v>
-      </c>
-      <c r="AJ5" t="s">
-        <v>95</v>
-      </c>
-      <c r="AK5" t="s">
-        <v>118</v>
-      </c>
-      <c r="AL5" t="s">
-        <v>119</v>
-      </c>
-      <c r="AM5" t="s">
-        <v>215</v>
-      </c>
-      <c r="AN5" t="s">
-        <v>120</v>
-      </c>
       <c r="AO5" t="s">
-        <v>94</v>
+        <v>72</v>
       </c>
     </row>
     <row r="6" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
+        <v>99</v>
+      </c>
+      <c r="B6" t="s">
+        <v>100</v>
+      </c>
+      <c r="C6" t="s">
+        <v>101</v>
+      </c>
+      <c r="D6" t="s">
+        <v>102</v>
+      </c>
+      <c r="E6" t="s">
+        <v>103</v>
+      </c>
+      <c r="F6" t="s">
+        <v>36</v>
+      </c>
+      <c r="G6" t="s">
+        <v>104</v>
+      </c>
+      <c r="H6" t="s">
+        <v>105</v>
+      </c>
+      <c r="I6" t="s">
+        <v>36</v>
+      </c>
+      <c r="J6" t="s">
+        <v>106</v>
+      </c>
+      <c r="K6" t="s">
+        <v>107</v>
+      </c>
+      <c r="L6" t="s">
+        <v>107</v>
+      </c>
+      <c r="M6" t="s">
+        <v>80</v>
+      </c>
+      <c r="N6" t="s">
+        <v>99</v>
+      </c>
+      <c r="O6" t="s">
+        <v>108</v>
+      </c>
+      <c r="P6" t="s">
+        <v>109</v>
+      </c>
+      <c r="Q6" t="s">
+        <v>36</v>
+      </c>
+      <c r="R6" t="s">
+        <v>110</v>
+      </c>
+      <c r="S6" t="s">
+        <v>111</v>
+      </c>
+      <c r="T6" t="s">
+        <v>39</v>
+      </c>
+      <c r="U6" t="s">
+        <v>107</v>
+      </c>
+      <c r="V6" t="s">
+        <v>103</v>
+      </c>
+      <c r="W6" t="s">
+        <v>112</v>
+      </c>
+      <c r="X6" t="s">
+        <v>113</v>
+      </c>
+      <c r="Y6" t="s">
+        <v>114</v>
+      </c>
+      <c r="Z6" t="s">
+        <v>115</v>
+      </c>
+      <c r="AA6" t="s">
+        <v>116</v>
+      </c>
+      <c r="AB6" t="s">
+        <v>117</v>
+      </c>
+      <c r="AC6" t="s">
+        <v>118</v>
+      </c>
+      <c r="AD6" t="s">
+        <v>42</v>
+      </c>
+      <c r="AE6" t="s">
+        <v>37</v>
+      </c>
+      <c r="AF6" t="s">
+        <v>117</v>
+      </c>
+      <c r="AG6" t="s">
+        <v>119</v>
+      </c>
+      <c r="AH6" t="s">
+        <v>120</v>
+      </c>
+      <c r="AI6" t="s">
+        <v>95</v>
+      </c>
+      <c r="AJ6" s="1">
+        <v>46177</v>
+      </c>
+      <c r="AK6" t="s">
         <v>121</v>
       </c>
-      <c r="B6" t="s">
+      <c r="AL6" t="s">
+        <v>44</v>
+      </c>
+      <c r="AM6" t="s">
+        <v>193</v>
+      </c>
+      <c r="AN6" t="s">
         <v>122</v>
       </c>
-      <c r="C6" t="s">
-        <v>123</v>
-      </c>
-      <c r="D6" t="s">
-        <v>124</v>
-      </c>
-      <c r="E6" t="s">
-        <v>125</v>
-      </c>
-      <c r="F6" t="s">
-        <v>41</v>
-      </c>
-      <c r="G6" t="s">
-        <v>126</v>
-      </c>
-      <c r="H6" t="s">
-        <v>127</v>
-      </c>
-      <c r="I6" t="s">
-        <v>41</v>
-      </c>
-      <c r="J6" t="s">
-        <v>128</v>
-      </c>
-      <c r="K6" t="s">
-        <v>129</v>
-      </c>
-      <c r="L6" t="s">
-        <v>129</v>
-      </c>
-      <c r="M6" t="s">
-        <v>102</v>
-      </c>
-      <c r="N6" t="s">
-        <v>121</v>
-      </c>
-      <c r="O6" t="s">
-        <v>130</v>
-      </c>
-      <c r="P6" t="s">
-        <v>131</v>
-      </c>
-      <c r="Q6" t="s">
-        <v>41</v>
-      </c>
-      <c r="R6" t="s">
-        <v>132</v>
-      </c>
-      <c r="S6" t="s">
-        <v>133</v>
-      </c>
-      <c r="T6" t="s">
-        <v>52</v>
-      </c>
-      <c r="U6" t="s">
-        <v>129</v>
-      </c>
-      <c r="V6" t="s">
-        <v>125</v>
-      </c>
-      <c r="W6" t="s">
-        <v>134</v>
-      </c>
-      <c r="X6" t="s">
-        <v>135</v>
-      </c>
-      <c r="Y6" t="s">
-        <v>136</v>
-      </c>
-      <c r="Z6" t="s">
-        <v>137</v>
-      </c>
-      <c r="AA6" t="s">
-        <v>138</v>
-      </c>
-      <c r="AB6" t="s">
-        <v>139</v>
-      </c>
-      <c r="AC6" t="s">
-        <v>140</v>
-      </c>
-      <c r="AD6" t="s">
-        <v>60</v>
-      </c>
-      <c r="AE6" t="s">
-        <v>42</v>
-      </c>
-      <c r="AF6" t="s">
-        <v>139</v>
-      </c>
-      <c r="AG6" t="s">
-        <v>141</v>
-      </c>
-      <c r="AH6" t="s">
-        <v>142</v>
-      </c>
-      <c r="AI6" t="s">
-        <v>117</v>
-      </c>
-      <c r="AJ6" t="s">
-        <v>122</v>
-      </c>
-      <c r="AK6" t="s">
-        <v>143</v>
-      </c>
-      <c r="AL6" t="s">
-        <v>65</v>
-      </c>
-      <c r="AM6" t="s">
-        <v>215</v>
-      </c>
-      <c r="AN6" t="s">
-        <v>144</v>
-      </c>
       <c r="AO6" t="s">
-        <v>121</v>
+        <v>99</v>
       </c>
     </row>
     <row r="7" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
+        <v>123</v>
+      </c>
+      <c r="B7" t="s">
+        <v>124</v>
+      </c>
+      <c r="C7" t="s">
+        <v>125</v>
+      </c>
+      <c r="D7" t="s">
+        <v>126</v>
+      </c>
+      <c r="E7" t="s">
+        <v>127</v>
+      </c>
+      <c r="F7" t="s">
+        <v>36</v>
+      </c>
+      <c r="G7" t="s">
+        <v>128</v>
+      </c>
+      <c r="H7" t="s">
+        <v>129</v>
+      </c>
+      <c r="I7" t="s">
+        <v>36</v>
+      </c>
+      <c r="J7" t="s">
+        <v>130</v>
+      </c>
+      <c r="K7" t="s">
+        <v>131</v>
+      </c>
+      <c r="L7" t="s">
+        <v>131</v>
+      </c>
+      <c r="M7" t="s">
+        <v>80</v>
+      </c>
+      <c r="N7" t="s">
+        <v>123</v>
+      </c>
+      <c r="O7" t="s">
+        <v>132</v>
+      </c>
+      <c r="P7" t="s">
+        <v>133</v>
+      </c>
+      <c r="Q7" t="s">
+        <v>36</v>
+      </c>
+      <c r="R7" t="s">
+        <v>134</v>
+      </c>
+      <c r="S7" t="s">
+        <v>135</v>
+      </c>
+      <c r="T7" t="s">
+        <v>59</v>
+      </c>
+      <c r="U7" t="s">
+        <v>131</v>
+      </c>
+      <c r="V7" t="s">
+        <v>127</v>
+      </c>
+      <c r="W7" t="s">
+        <v>136</v>
+      </c>
+      <c r="X7" t="s">
+        <v>40</v>
+      </c>
+      <c r="Y7" t="s">
+        <v>137</v>
+      </c>
+      <c r="Z7" t="s">
+        <v>138</v>
+      </c>
+      <c r="AA7" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB7" t="s">
+        <v>139</v>
+      </c>
+      <c r="AC7" t="s">
+        <v>140</v>
+      </c>
+      <c r="AD7" t="s">
+        <v>42</v>
+      </c>
+      <c r="AE7" t="s">
+        <v>37</v>
+      </c>
+      <c r="AF7" t="s">
+        <v>141</v>
+      </c>
+      <c r="AG7" t="s">
+        <v>142</v>
+      </c>
+      <c r="AH7" t="s">
+        <v>143</v>
+      </c>
+      <c r="AI7" t="s">
+        <v>144</v>
+      </c>
+      <c r="AJ7" s="1">
+        <v>46178</v>
+      </c>
+      <c r="AK7" t="s">
         <v>145</v>
       </c>
-      <c r="B7" t="s">
+      <c r="AL7" t="s">
         <v>146</v>
       </c>
-      <c r="C7" t="s">
+      <c r="AM7" t="s">
+        <v>193</v>
+      </c>
+      <c r="AN7" t="s">
         <v>147</v>
       </c>
-      <c r="D7" t="s">
-        <v>148</v>
-      </c>
-      <c r="E7" t="s">
-        <v>149</v>
-      </c>
-      <c r="F7" t="s">
-        <v>41</v>
-      </c>
-      <c r="G7" t="s">
-        <v>150</v>
-      </c>
-      <c r="H7" t="s">
-        <v>151</v>
-      </c>
-      <c r="I7" t="s">
-        <v>41</v>
-      </c>
-      <c r="J7" t="s">
-        <v>152</v>
-      </c>
-      <c r="K7" t="s">
-        <v>153</v>
-      </c>
-      <c r="L7" t="s">
-        <v>153</v>
-      </c>
-      <c r="M7" t="s">
-        <v>102</v>
-      </c>
-      <c r="N7" t="s">
-        <v>145</v>
-      </c>
-      <c r="O7" t="s">
-        <v>154</v>
-      </c>
-      <c r="P7" t="s">
-        <v>155</v>
-      </c>
-      <c r="Q7" t="s">
-        <v>41</v>
-      </c>
-      <c r="R7" t="s">
-        <v>156</v>
-      </c>
-      <c r="S7" t="s">
-        <v>157</v>
-      </c>
-      <c r="T7" t="s">
-        <v>81</v>
-      </c>
-      <c r="U7" t="s">
-        <v>153</v>
-      </c>
-      <c r="V7" t="s">
-        <v>149</v>
-      </c>
-      <c r="W7" t="s">
-        <v>158</v>
-      </c>
-      <c r="X7" t="s">
-        <v>54</v>
-      </c>
-      <c r="Y7" t="s">
-        <v>159</v>
-      </c>
-      <c r="Z7" t="s">
-        <v>160</v>
-      </c>
-      <c r="AA7" t="s">
-        <v>57</v>
-      </c>
-      <c r="AB7" t="s">
-        <v>161</v>
-      </c>
-      <c r="AC7" t="s">
-        <v>162</v>
-      </c>
-      <c r="AD7" t="s">
-        <v>60</v>
-      </c>
-      <c r="AE7" t="s">
-        <v>42</v>
-      </c>
-      <c r="AF7" t="s">
-        <v>163</v>
-      </c>
-      <c r="AG7" t="s">
-        <v>164</v>
-      </c>
-      <c r="AH7" t="s">
-        <v>165</v>
-      </c>
-      <c r="AI7" t="s">
-        <v>166</v>
-      </c>
-      <c r="AJ7" t="s">
-        <v>146</v>
-      </c>
-      <c r="AK7" t="s">
-        <v>167</v>
-      </c>
-      <c r="AL7" t="s">
-        <v>168</v>
-      </c>
-      <c r="AM7" t="s">
-        <v>215</v>
-      </c>
-      <c r="AN7" t="s">
-        <v>169</v>
-      </c>
       <c r="AO7" t="s">
-        <v>145</v>
+        <v>123</v>
       </c>
     </row>
     <row r="8" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>170</v>
+        <v>148</v>
       </c>
       <c r="B8" t="s">
-        <v>171</v>
+        <v>149</v>
       </c>
       <c r="C8" t="s">
-        <v>172</v>
+        <v>150</v>
       </c>
       <c r="D8" t="s">
-        <v>173</v>
+        <v>151</v>
       </c>
       <c r="E8" t="s">
-        <v>174</v>
+        <v>152</v>
       </c>
       <c r="F8" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="G8" t="s">
-        <v>175</v>
+        <v>153</v>
       </c>
       <c r="H8" t="s">
-        <v>176</v>
+        <v>154</v>
       </c>
       <c r="I8" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="J8" t="s">
-        <v>177</v>
+        <v>155</v>
       </c>
       <c r="K8" t="s">
-        <v>178</v>
+        <v>156</v>
       </c>
       <c r="L8" t="s">
-        <v>178</v>
+        <v>156</v>
       </c>
       <c r="M8" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="N8" t="s">
-        <v>170</v>
+        <v>148</v>
       </c>
       <c r="O8" t="s">
-        <v>179</v>
+        <v>157</v>
       </c>
       <c r="P8" t="s">
-        <v>180</v>
+        <v>158</v>
       </c>
       <c r="Q8" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="R8" t="s">
-        <v>181</v>
+        <v>159</v>
       </c>
       <c r="S8" t="s">
-        <v>182</v>
+        <v>160</v>
       </c>
       <c r="T8" t="s">
-        <v>52</v>
+        <v>39</v>
       </c>
       <c r="U8" t="s">
-        <v>178</v>
+        <v>156</v>
       </c>
       <c r="V8" t="s">
-        <v>174</v>
+        <v>152</v>
       </c>
       <c r="W8" t="s">
-        <v>183</v>
+        <v>161</v>
       </c>
       <c r="X8" t="s">
-        <v>108</v>
+        <v>86</v>
       </c>
       <c r="Y8" t="s">
-        <v>184</v>
+        <v>162</v>
       </c>
       <c r="Z8" t="s">
-        <v>185</v>
+        <v>163</v>
       </c>
       <c r="AA8" t="s">
-        <v>86</v>
+        <v>64</v>
       </c>
       <c r="AB8" t="s">
-        <v>186</v>
+        <v>164</v>
       </c>
       <c r="AC8" t="s">
-        <v>187</v>
+        <v>165</v>
       </c>
       <c r="AD8" t="s">
-        <v>60</v>
+        <v>42</v>
       </c>
       <c r="AE8" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="AF8" t="s">
-        <v>186</v>
+        <v>164</v>
       </c>
       <c r="AG8" t="s">
-        <v>188</v>
+        <v>166</v>
       </c>
       <c r="AH8" t="s">
-        <v>189</v>
+        <v>167</v>
       </c>
       <c r="AI8" t="s">
-        <v>166</v>
-      </c>
-      <c r="AJ8" t="s">
-        <v>171</v>
+        <v>144</v>
+      </c>
+      <c r="AJ8" s="1">
+        <v>46179</v>
       </c>
       <c r="AK8" t="s">
-        <v>190</v>
+        <v>168</v>
       </c>
       <c r="AL8" t="s">
-        <v>92</v>
+        <v>70</v>
       </c>
       <c r="AM8" t="s">
-        <v>215</v>
+        <v>193</v>
       </c>
       <c r="AN8" t="s">
-        <v>191</v>
+        <v>169</v>
       </c>
       <c r="AO8" t="s">
-        <v>170</v>
+        <v>148</v>
       </c>
     </row>
     <row r="9" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
+        <v>170</v>
+      </c>
+      <c r="B9" t="s">
+        <v>171</v>
+      </c>
+      <c r="C9" t="s">
+        <v>172</v>
+      </c>
+      <c r="D9" t="s">
+        <v>173</v>
+      </c>
+      <c r="E9" t="s">
+        <v>174</v>
+      </c>
+      <c r="F9" t="s">
+        <v>36</v>
+      </c>
+      <c r="G9" t="s">
+        <v>175</v>
+      </c>
+      <c r="H9" t="s">
+        <v>176</v>
+      </c>
+      <c r="I9" t="s">
+        <v>177</v>
+      </c>
+      <c r="J9" t="s">
+        <v>178</v>
+      </c>
+      <c r="K9" t="s">
+        <v>179</v>
+      </c>
+      <c r="L9" t="s">
+        <v>179</v>
+      </c>
+      <c r="M9" t="s">
+        <v>38</v>
+      </c>
+      <c r="N9" t="s">
+        <v>170</v>
+      </c>
+      <c r="O9" t="s">
+        <v>180</v>
+      </c>
+      <c r="P9" t="s">
+        <v>176</v>
+      </c>
+      <c r="Q9" t="s">
+        <v>177</v>
+      </c>
+      <c r="R9" t="s">
+        <v>176</v>
+      </c>
+      <c r="S9" t="s">
+        <v>181</v>
+      </c>
+      <c r="T9" t="s">
+        <v>39</v>
+      </c>
+      <c r="U9" t="s">
+        <v>179</v>
+      </c>
+      <c r="V9" t="s">
+        <v>174</v>
+      </c>
+      <c r="W9" t="s">
+        <v>182</v>
+      </c>
+      <c r="X9" t="s">
+        <v>61</v>
+      </c>
+      <c r="Y9" t="s">
+        <v>183</v>
+      </c>
+      <c r="Z9" t="s">
+        <v>184</v>
+      </c>
+      <c r="AA9" t="s">
+        <v>185</v>
+      </c>
+      <c r="AB9" t="s">
+        <v>90</v>
+      </c>
+      <c r="AC9" t="s">
+        <v>186</v>
+      </c>
+      <c r="AD9" t="s">
+        <v>42</v>
+      </c>
+      <c r="AE9" t="s">
+        <v>37</v>
+      </c>
+      <c r="AF9" t="s">
+        <v>92</v>
+      </c>
+      <c r="AG9" t="s">
+        <v>187</v>
+      </c>
+      <c r="AH9" t="s">
+        <v>188</v>
+      </c>
+      <c r="AI9" t="s">
+        <v>189</v>
+      </c>
+      <c r="AJ9" s="1">
+        <v>46180</v>
+      </c>
+      <c r="AK9" t="s">
+        <v>190</v>
+      </c>
+      <c r="AL9" t="s">
+        <v>191</v>
+      </c>
+      <c r="AM9" t="s">
+        <v>193</v>
+      </c>
+      <c r="AN9" t="s">
         <v>192</v>
       </c>
-      <c r="B9" t="s">
-        <v>193</v>
-      </c>
-      <c r="C9" t="s">
-        <v>194</v>
-      </c>
-      <c r="D9" t="s">
-        <v>195</v>
-      </c>
-      <c r="E9" t="s">
-        <v>196</v>
-      </c>
-      <c r="F9" t="s">
-        <v>41</v>
-      </c>
-      <c r="G9" t="s">
-        <v>197</v>
-      </c>
-      <c r="H9" t="s">
-        <v>198</v>
-      </c>
-      <c r="I9" t="s">
-        <v>199</v>
-      </c>
-      <c r="J9" t="s">
-        <v>200</v>
-      </c>
-      <c r="K9" t="s">
-        <v>201</v>
-      </c>
-      <c r="L9" t="s">
-        <v>201</v>
-      </c>
-      <c r="M9" t="s">
-        <v>47</v>
-      </c>
-      <c r="N9" t="s">
-        <v>192</v>
-      </c>
-      <c r="O9" t="s">
-        <v>202</v>
-      </c>
-      <c r="P9" t="s">
-        <v>198</v>
-      </c>
-      <c r="Q9" t="s">
-        <v>199</v>
-      </c>
-      <c r="R9" t="s">
-        <v>198</v>
-      </c>
-      <c r="S9" t="s">
-        <v>203</v>
-      </c>
-      <c r="T9" t="s">
-        <v>52</v>
-      </c>
-      <c r="U9" t="s">
-        <v>201</v>
-      </c>
-      <c r="V9" t="s">
-        <v>196</v>
-      </c>
-      <c r="W9" t="s">
-        <v>204</v>
-      </c>
-      <c r="X9" t="s">
-        <v>83</v>
-      </c>
-      <c r="Y9" t="s">
-        <v>205</v>
-      </c>
-      <c r="Z9" t="s">
-        <v>206</v>
-      </c>
-      <c r="AA9" t="s">
-        <v>207</v>
-      </c>
-      <c r="AB9" t="s">
-        <v>112</v>
-      </c>
-      <c r="AC9" t="s">
-        <v>208</v>
-      </c>
-      <c r="AD9" t="s">
-        <v>60</v>
-      </c>
-      <c r="AE9" t="s">
-        <v>42</v>
-      </c>
-      <c r="AF9" t="s">
-        <v>114</v>
-      </c>
-      <c r="AG9" t="s">
-        <v>209</v>
-      </c>
-      <c r="AH9" t="s">
-        <v>210</v>
-      </c>
-      <c r="AI9" t="s">
-        <v>211</v>
-      </c>
-      <c r="AJ9" t="s">
-        <v>193</v>
-      </c>
-      <c r="AK9" t="s">
-        <v>212</v>
-      </c>
-      <c r="AL9" t="s">
-        <v>213</v>
-      </c>
-      <c r="AM9" t="s">
-        <v>215</v>
-      </c>
-      <c r="AN9" t="s">
-        <v>214</v>
-      </c>
       <c r="AO9" t="s">
-        <v>192</v>
-      </c>
+        <v>170</v>
+      </c>
+    </row>
+    <row r="10" spans="1:41" x14ac:dyDescent="0.25">
+      <c r="AJ10" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="A2:AO2 A1:AI1 AK1:AO1 A4:AL9 A3:AI3 AK3:AL3 AN3:AO3 AN4:AO9" numberStoredAsText="1"/>
+    <ignoredError sqref="A2:AO2 A1:AI1 AK1:AO1 A5:AI9 AN4:AO9 A4:AI4 AK4:AL4 AK5:AL9" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>